--- a/data/trans_dic/P3A_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,06; 18,67</t>
+          <t>12,84; 18,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,04</t>
+          <t>22,15; 28,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,18; 31,19</t>
+          <t>23,95; 30,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,17; 29,31</t>
+          <t>22,2; 29,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,74</t>
+          <t>9,05; 13,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,97</t>
+          <t>9,54; 14,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 16,31</t>
+          <t>11,15; 16,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,01; 23,41</t>
+          <t>15,99; 23,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 15,48</t>
+          <t>11,63; 15,3</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,69; 21,05</t>
+          <t>16,48; 20,92</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,31; 22,84</t>
+          <t>18,37; 22,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,12; 25,51</t>
+          <t>19,82; 25,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,41; 22,94</t>
+          <t>17,11; 22,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,81; 30,62</t>
+          <t>24,49; 30,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,54; 34,63</t>
+          <t>28,67; 34,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 30,49</t>
+          <t>11,73; 30,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,28; 12,57</t>
+          <t>8,5; 12,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 16,26</t>
+          <t>11,85; 16,17</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,23; 22,24</t>
+          <t>16,83; 21,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,63; 26,37</t>
+          <t>21,74; 26,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 16,75</t>
+          <t>13,32; 16,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 22,68</t>
+          <t>18,76; 22,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,38; 27,47</t>
+          <t>23,52; 27,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 27,29</t>
+          <t>15,77; 27,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,18; 28,14</t>
+          <t>20,94; 27,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,11; 30,0</t>
+          <t>23,2; 30,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,35; 36,33</t>
+          <t>29,0; 36,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,47; 36,31</t>
+          <t>28,24; 36,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,54; 16,96</t>
+          <t>11,7; 16,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 19,3</t>
+          <t>13,59; 19,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,25; 23,88</t>
+          <t>18,06; 23,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,1; 24,49</t>
+          <t>9,31; 24,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 21,62</t>
+          <t>17,05; 21,47</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,2; 23,66</t>
+          <t>19,29; 23,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,26; 29,11</t>
+          <t>24,48; 29,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,63; 28,49</t>
+          <t>16,35; 28,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,49; 25,83</t>
+          <t>20,69; 26,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,31; 32,5</t>
+          <t>26,49; 32,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,46; 39,48</t>
+          <t>33,38; 39,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,36; 31,55</t>
+          <t>25,0; 31,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,03</t>
+          <t>10,89; 14,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 19,33</t>
+          <t>14,51; 19,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 21,83</t>
+          <t>16,83; 21,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,67; 19,24</t>
+          <t>13,66; 19,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 19,74</t>
+          <t>16,29; 19,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 24,86</t>
+          <t>20,81; 24,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,58; 29,54</t>
+          <t>25,66; 29,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,7; 24,13</t>
+          <t>19,63; 24,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,39; 22,27</t>
+          <t>19,56; 22,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 29,0</t>
+          <t>25,84; 29,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,85; 34,21</t>
+          <t>30,71; 34,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,19; 29,56</t>
+          <t>21,24; 29,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,14</t>
+          <t>11,0; 13,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 16,09</t>
+          <t>13,71; 16,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,28; 19,96</t>
+          <t>17,24; 19,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,28; 21,65</t>
+          <t>15,97; 21,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,22</t>
+          <t>15,48; 17,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,02; 22,05</t>
+          <t>20,05; 22,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,19; 26,37</t>
+          <t>24,2; 26,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,2; 25,03</t>
+          <t>20,28; 25,16</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que las tareas domésticas las realiza principalmente el/la entrevistado/a junto con su pareja</t>
+          <t>Hogares en los que las tareas domésticas las realiza principalmente la persona entrevistada junto con su pareja (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90612; 129604</t>
+          <t>89088; 129050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>156615; 204281</t>
+          <t>155841; 202576</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163138; 210478</t>
+          <t>161648; 208819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140787; 186095</t>
+          <t>140996; 185340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62764; 94426</t>
+          <t>62184; 95249</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66923; 104345</t>
+          <t>66478; 101763</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>73269; 109592</t>
+          <t>74912; 108825</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>116101; 169831</t>
+          <t>115945; 168433</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>163071; 213796</t>
+          <t>160701; 211293</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>233745; 294816</t>
+          <t>230855; 292983</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>246569; 307531</t>
+          <t>247451; 306258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>273667; 346947</t>
+          <t>269633; 344287</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>167410; 220639</t>
+          <t>164563; 217060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>252259; 311419</t>
+          <t>248997; 310024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>291557; 353730</t>
+          <t>292876; 355865</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>151332; 363708</t>
+          <t>139900; 362430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>80171; 121705</t>
+          <t>82300; 120021</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>121434; 167858</t>
+          <t>122343; 166862</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>179552; 231731</t>
+          <t>175365; 228406</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>207341; 252793</t>
+          <t>208415; 252893</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>260128; 323278</t>
+          <t>257008; 324827</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>386444; 464645</t>
+          <t>384453; 463155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>482445; 566904</t>
+          <t>485364; 565253</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>346775; 587163</t>
+          <t>339202; 587291</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>143700; 190906</t>
+          <t>142112; 188144</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175110; 227298</t>
+          <t>175737; 228565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>221789; 274515</t>
+          <t>219155; 274376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>200624; 255838</t>
+          <t>199014; 254903</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>78522; 115429</t>
+          <t>79596; 115028</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104882; 149629</t>
+          <t>105324; 148990</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>142906; 186954</t>
+          <t>141414; 186193</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94239; 228623</t>
+          <t>86939; 227094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>232319; 293802</t>
+          <t>231697; 291784</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>294281; 362641</t>
+          <t>295673; 360113</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>373358; 447951</t>
+          <t>376738; 446755</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>256033; 466731</t>
+          <t>267796; 471670</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>192867; 243166</t>
+          <t>194774; 247316</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>249356; 307996</t>
+          <t>251050; 310948</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312290; 368506</t>
+          <t>311546; 372990</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>234867; 292226</t>
+          <t>231569; 290280</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>111401; 156152</t>
+          <t>113141; 155473</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>155912; 203305</t>
+          <t>152642; 202236</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>176472; 227650</t>
+          <t>175534; 226727</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149554; 210387</t>
+          <t>149385; 211652</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>321045; 390937</t>
+          <t>322590; 386527</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>418171; 497036</t>
+          <t>416074; 497260</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>505527; 583681</t>
+          <t>507023; 584286</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>397820; 487366</t>
+          <t>396494; 487392</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>635310; 729493</t>
+          <t>640571; 736856</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>886882; 993468</t>
+          <t>885148; 996643</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1044449; 1158096</t>
+          <t>1039782; 1155736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>732759; 1022406</t>
+          <t>734467; 1027734</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>367940; 443267</t>
+          <t>371045; 445792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>482746; 572044</t>
+          <t>487569; 570891</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>611538; 706442</t>
+          <t>610279; 703337</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>604305; 803283</t>
+          <t>592589; 809525</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1031181; 1145058</t>
+          <t>1029471; 1154499</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1397854; 1539790</t>
+          <t>1400238; 1548024</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1674992; 1826342</t>
+          <t>1676119; 1828966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1448600; 1794625</t>
+          <t>1453819; 1803776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R1-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R1-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,84; 18,59</t>
+          <t>13,03; 18,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,15; 28,8</t>
+          <t>22,22; 29,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,95; 30,95</t>
+          <t>24,44; 31,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22,2; 29,19</t>
+          <t>22,31; 29,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,86</t>
+          <t>9,04; 13,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,6</t>
+          <t>9,72; 14,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 16,2</t>
+          <t>10,65; 16,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 23,22</t>
+          <t>19,2; 24,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 15,3</t>
+          <t>11,78; 15,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,48; 20,92</t>
+          <t>16,73; 21,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18,37; 22,74</t>
+          <t>18,39; 22,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,82; 25,31</t>
+          <t>21,38; 25,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>26,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,11; 22,57</t>
+          <t>17,46; 22,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,49; 30,49</t>
+          <t>24,88; 30,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,67; 34,84</t>
+          <t>28,54; 34,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11,73; 30,38</t>
+          <t>26,33; 32,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,39</t>
+          <t>8,29; 12,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 16,17</t>
+          <t>11,77; 16,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,92</t>
+          <t>17,02; 22,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,74; 26,38</t>
+          <t>20,85; 25,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,32; 16,83</t>
+          <t>13,38; 16,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,76; 22,6</t>
+          <t>18,94; 22,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,52; 27,39</t>
+          <t>23,56; 27,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 27,3</t>
+          <t>24,49; 28,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>27,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 27,73</t>
+          <t>20,73; 27,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 30,17</t>
+          <t>22,8; 30,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29,0; 36,31</t>
+          <t>29,35; 36,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,24; 36,17</t>
+          <t>28,67; 35,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,7; 16,9</t>
+          <t>11,41; 16,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,59; 19,22</t>
+          <t>13,7; 19,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,06; 23,78</t>
+          <t>18,13; 24,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 24,33</t>
+          <t>21,04; 26,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,05; 21,47</t>
+          <t>16,85; 21,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,29; 23,49</t>
+          <t>19,06; 23,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,48; 29,04</t>
+          <t>24,56; 29,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 28,79</t>
+          <t>25,7; 30,15</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>20,69; 26,27</t>
+          <t>20,96; 26,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26,49; 32,81</t>
+          <t>26,36; 32,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,38; 39,96</t>
+          <t>33,47; 39,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25,0; 31,34</t>
+          <t>25,43; 31,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,97</t>
+          <t>10,82; 14,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,51; 19,23</t>
+          <t>14,52; 19,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,83; 21,74</t>
+          <t>16,95; 21,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 19,35</t>
+          <t>15,96; 19,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,29; 19,52</t>
+          <t>16,09; 19,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20,81; 24,87</t>
+          <t>20,82; 24,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 29,57</t>
+          <t>25,63; 29,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,63; 24,13</t>
+          <t>20,98; 24,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,56; 22,49</t>
+          <t>19,52; 22,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>25,84; 29,09</t>
+          <t>25,79; 29,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30,71; 34,14</t>
+          <t>30,9; 34,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21,24; 29,71</t>
+          <t>27,31; 30,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,0; 13,21</t>
+          <t>10,89; 13,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,71; 16,05</t>
+          <t>13,77; 16,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,24; 19,87</t>
+          <t>17,19; 19,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,97; 21,81</t>
+          <t>20,1; 22,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15,48; 17,36</t>
+          <t>15,46; 17,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,05; 22,17</t>
+          <t>20,1; 22,11</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,2; 26,41</t>
+          <t>24,29; 26,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,16</t>
+          <t>24,01; 26,1</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>162605</t>
+          <t>176500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>149290</t>
+          <t>158025</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>334525</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89088; 129050</t>
+          <t>90435; 129147</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>155841; 202576</t>
+          <t>156290; 204638</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>161648; 208819</t>
+          <t>164906; 211311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140996; 185340</t>
+          <t>153976; 202660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62184; 95249</t>
+          <t>62103; 94391</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66478; 101763</t>
+          <t>67775; 102943</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>74912; 108825</t>
+          <t>71580; 107998</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>115945; 168433</t>
+          <t>140968; 176357</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>160701; 211293</t>
+          <t>162712; 213527</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>230855; 292983</t>
+          <t>234328; 294292</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247451; 306258</t>
+          <t>247698; 306451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>269633; 344287</t>
+          <t>304517; 365146</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279557</t>
+          <t>309900</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>230190</t>
+          <t>247464</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>509747</t>
+          <t>557364</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>164563; 217060</t>
+          <t>167965; 218783</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>248997; 310024</t>
+          <t>252953; 312113</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>292876; 355865</t>
+          <t>291481; 352930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139900; 362430</t>
+          <t>276156; 343326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82300; 120021</t>
+          <t>80279; 121652</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>122343; 166862</t>
+          <t>121487; 166463</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>175365; 228406</t>
+          <t>177311; 230719</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>208415; 252893</t>
+          <t>223366; 270992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>257008; 324827</t>
+          <t>258304; 324690</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>384453; 463155</t>
+          <t>388110; 469307</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>485364; 565253</t>
+          <t>486089; 565829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>339202; 587291</t>
+          <t>519319; 601488</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>227488</t>
+          <t>259294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>169661</t>
+          <t>191692</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>397150</t>
+          <t>450986</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142112; 188144</t>
+          <t>140652; 189483</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>175737; 228565</t>
+          <t>172709; 227449</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219155; 274376</t>
+          <t>221761; 273586</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>199014; 254903</t>
+          <t>230270; 288585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>79596; 115028</t>
+          <t>77630; 113262</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>105324; 148990</t>
+          <t>106228; 149231</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>141414; 186193</t>
+          <t>141974; 189309</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86939; 227094</t>
+          <t>170893; 215507</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>231697; 291784</t>
+          <t>228983; 290267</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>295673; 360113</t>
+          <t>292197; 360438</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>376738; 446755</t>
+          <t>377882; 447086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>267796; 471670</t>
+          <t>415141; 486967</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262580</t>
+          <t>279565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>199839</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>448766</t>
+          <t>479404</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194774; 247316</t>
+          <t>197315; 248030</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>251050; 310948</t>
+          <t>249836; 310331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311546; 372990</t>
+          <t>312401; 372338</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>231569; 290280</t>
+          <t>251601; 308866</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>113141; 155473</t>
+          <t>112414; 155431</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>152642; 202236</t>
+          <t>152692; 202962</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175534; 226727</t>
+          <t>176749; 228945</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>149385; 211652</t>
+          <t>178380; 221249</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>322590; 386527</t>
+          <t>318596; 387554</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>416074; 497260</t>
+          <t>416407; 495942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>507023; 584286</t>
+          <t>506526; 581756</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>396494; 487392</t>
+          <t>442102; 514827</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>932230</t>
+          <t>1025259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>735328</t>
+          <t>797020</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1667558</t>
+          <t>1822280</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>640571; 736856</t>
+          <t>639436; 734655</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>885148; 996643</t>
+          <t>883601; 998295</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1039782; 1155736</t>
+          <t>1046073; 1157803</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>734467; 1027734</t>
+          <t>964591; 1085978</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>371045; 445792</t>
+          <t>367576; 444153</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>487569; 570891</t>
+          <t>489634; 579077</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>610279; 703337</t>
+          <t>608342; 703798</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>592589; 809525</t>
+          <t>750751; 837236</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1029471; 1154499</t>
+          <t>1027807; 1148678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1400238; 1548024</t>
+          <t>1403293; 1543968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1676119; 1828966</t>
+          <t>1681725; 1826660</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1453819; 1803776</t>
+          <t>1744970; 1897108</t>
         </is>
       </c>
     </row>
